--- a/results/Supplementary_Table_4_BUSTED_PH.xlsx
+++ b/results/Supplementary_Table_4_BUSTED_PH.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/calvin/orb-selection/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54C6B9B6-A15B-7E46-ACBC-8C2561307D2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1E75880-0E20-F040-B2AB-9B9E54AD243C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1040" yWindow="600" windowWidth="43760" windowHeight="24600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7283,6 +7283,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.1640625" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="65.6640625" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="71.5" bestFit="1" customWidth="1"/>
   </cols>
@@ -14130,7 +14131,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="73" spans="1:32" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>590</v>
       </c>
@@ -14224,7 +14225,6 @@
       <c r="AE73" t="s">
         <v>597</v>
       </c>
-      <c r="AF73"/>
     </row>
     <row r="74" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
@@ -14606,9 +14606,7 @@
       <c r="AE77" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="AF77" s="2">
-        <v>1</v>
-      </c>
+      <c r="AF77" s="2"/>
     </row>
     <row r="78" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
@@ -15075,9 +15073,7 @@
       <c r="AE82" s="2" t="s">
         <v>2109</v>
       </c>
-      <c r="AF82" s="2">
-        <v>1</v>
-      </c>
+      <c r="AF82" s="2"/>
     </row>
     <row r="83" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
@@ -19896,9 +19892,7 @@
       <c r="AE133" s="2" t="s">
         <v>1743</v>
       </c>
-      <c r="AF133" s="2">
-        <v>1</v>
-      </c>
+      <c r="AF133" s="2"/>
     </row>
     <row r="134" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
@@ -23690,9 +23684,7 @@
       <c r="AE173" s="2" t="s">
         <v>1976</v>
       </c>
-      <c r="AF173" s="2">
-        <v>1</v>
-      </c>
+      <c r="AF173" s="2"/>
     </row>
     <row r="174" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
@@ -25594,9 +25586,7 @@
       <c r="AE193" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="AF193" s="2">
-        <v>1</v>
-      </c>
+      <c r="AF193" s="2"/>
     </row>
     <row r="194" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
@@ -26452,9 +26442,7 @@
       <c r="AE202" s="2" t="s">
         <v>543</v>
       </c>
-      <c r="AF202" s="2">
-        <v>1</v>
-      </c>
+      <c r="AF202" s="2"/>
     </row>
     <row r="203" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
@@ -27596,98 +27584,98 @@
         <v>1914</v>
       </c>
     </row>
-    <row r="215" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A215" t="s">
+    <row r="215" spans="1:31" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A215" s="2" t="s">
         <v>2008</v>
       </c>
-      <c r="B215" t="s">
+      <c r="B215" s="2" t="s">
         <v>663</v>
       </c>
-      <c r="C215">
-        <v>0</v>
-      </c>
-      <c r="D215">
+      <c r="C215" s="2">
+        <v>0</v>
+      </c>
+      <c r="D215" s="2">
         <v>151.78451276288251</v>
       </c>
-      <c r="E215">
+      <c r="E215" s="2">
         <v>0.27401249457192711</v>
       </c>
-      <c r="F215">
+      <c r="F215" s="2">
         <v>1.2028687848069239</v>
       </c>
-      <c r="G215">
-        <v>0</v>
-      </c>
-      <c r="H215">
+      <c r="G215" s="2">
+        <v>0</v>
+      </c>
+      <c r="H215" s="2">
         <v>105.77577783461309</v>
       </c>
-      <c r="I215">
+      <c r="I215" s="2">
         <v>6.2924396276527159E-5</v>
       </c>
-      <c r="J215">
+      <c r="J215" s="2">
         <v>5.3051305331526072E-5</v>
       </c>
-      <c r="K215">
+      <c r="K215" s="2">
         <v>5.9469017039404494E-3</v>
       </c>
-      <c r="L215">
+      <c r="L215" s="2">
         <v>0.39147671574423931</v>
       </c>
-      <c r="M215">
+      <c r="M215" s="2">
         <v>0.31871051636073178</v>
       </c>
-      <c r="N215">
+      <c r="N215" s="2">
         <v>0.56100873656089634</v>
       </c>
-      <c r="O215">
+      <c r="O215" s="2">
         <v>6.9855518857173431</v>
       </c>
-      <c r="P215">
+      <c r="P215" s="2">
         <v>4.7514547694864351E-2</v>
       </c>
-      <c r="Q215">
+      <c r="Q215" s="2">
         <v>6.5733125345135549E-2</v>
       </c>
-      <c r="R215">
+      <c r="R215" s="2">
         <v>0.77888688323986166</v>
       </c>
-      <c r="S215">
+      <c r="S215" s="2">
         <v>1</v>
       </c>
-      <c r="T215">
+      <c r="T215" s="2">
         <v>0.21836976508669911</v>
       </c>
-      <c r="U215">
+      <c r="U215" s="2">
         <v>315.00251121989658</v>
       </c>
-      <c r="V215">
+      <c r="V215" s="2">
         <v>2.7433516734391961E-3</v>
       </c>
-      <c r="W215">
+      <c r="W215" s="2">
         <v>0.51304279590898383</v>
       </c>
-      <c r="X215">
+      <c r="X215" s="2">
         <v>1.133731100505039</v>
       </c>
-      <c r="Y215" t="s">
+      <c r="Y215" s="2" t="s">
         <v>2009</v>
       </c>
-      <c r="Z215" t="s">
+      <c r="Z215" s="2" t="s">
         <v>2010</v>
       </c>
-      <c r="AA215" t="s">
+      <c r="AA215" s="2" t="s">
         <v>2011</v>
       </c>
-      <c r="AB215" t="s">
+      <c r="AB215" s="2" t="s">
         <v>2012</v>
       </c>
-      <c r="AC215" t="s">
+      <c r="AC215" s="2" t="s">
         <v>2013</v>
       </c>
-      <c r="AD215" t="s">
+      <c r="AD215" s="2" t="s">
         <v>2014</v>
       </c>
-      <c r="AE215" t="s">
+      <c r="AE215" s="2" t="s">
         <v>2015</v>
       </c>
     </row>
@@ -31269,9 +31257,7 @@
       <c r="AE253" s="2" t="s">
         <v>524</v>
       </c>
-      <c r="AF253" s="2">
-        <v>1</v>
-      </c>
+      <c r="AF253" s="2"/>
     </row>
     <row r="254" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
@@ -31749,100 +31735,99 @@
       </c>
     </row>
     <row r="259" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A259" s="3" t="s">
+      <c r="A259" t="s">
         <v>500</v>
       </c>
-      <c r="B259" s="3" t="s">
+      <c r="B259" t="s">
         <v>32</v>
       </c>
-      <c r="C259" s="3">
+      <c r="C259">
         <v>5.427545659426658E-3</v>
       </c>
-      <c r="D259" s="3">
+      <c r="D259">
         <v>9.0462421262636781</v>
       </c>
-      <c r="E259" s="3">
+      <c r="E259">
         <v>0.5</v>
       </c>
-      <c r="F259" s="3">
-        <v>0</v>
-      </c>
-      <c r="G259" s="3">
+      <c r="F259">
+        <v>0</v>
+      </c>
+      <c r="G259">
         <v>4.7099837269564133E-2</v>
       </c>
-      <c r="H259" s="3">
+      <c r="H259">
         <v>11.22484206684749</v>
       </c>
-      <c r="I259" s="3">
+      <c r="I259">
         <v>0.1105891934003311</v>
       </c>
-      <c r="J259" s="3">
+      <c r="J259">
         <v>9.3706929362941754E-2</v>
       </c>
-      <c r="K259" s="3">
+      <c r="K259">
         <v>1.4534775122776769E-2</v>
       </c>
-      <c r="L259" s="3">
+      <c r="L259">
         <v>0.83850308730458178</v>
       </c>
-      <c r="M259" s="3">
+      <c r="M259">
         <v>0.19743618631625659</v>
       </c>
-      <c r="N259" s="3">
+      <c r="N259">
         <v>0.1611326589436157</v>
       </c>
-      <c r="O259" s="3">
+      <c r="O259">
         <v>40.222747481718947</v>
       </c>
-      <c r="P259" s="3">
+      <c r="P259">
         <v>3.6425375180252549E-4</v>
       </c>
-      <c r="Q259" s="3">
+      <c r="Q259">
         <v>1.8145900571712521E-2</v>
       </c>
-      <c r="R259" s="3">
+      <c r="R259">
         <v>0.80989141630870676</v>
       </c>
-      <c r="S259" s="3">
+      <c r="S259">
         <v>8.8689131047228822E-2</v>
       </c>
-      <c r="T259" s="3">
+      <c r="T259">
         <v>0.1573758387866864</v>
       </c>
-      <c r="U259" s="3">
+      <c r="U259">
         <v>0.7032009150913322</v>
       </c>
-      <c r="V259" s="3">
+      <c r="V259">
         <v>3.27327449046068E-2</v>
       </c>
-      <c r="W259" s="3">
+      <c r="W259">
         <v>5.8652158164573392E-2</v>
       </c>
-      <c r="X259" s="3">
+      <c r="X259">
         <v>5.167143167441185E-2</v>
       </c>
-      <c r="Y259" s="3" t="s">
+      <c r="Y259" t="s">
         <v>501</v>
       </c>
-      <c r="Z259" s="3" t="s">
+      <c r="Z259" t="s">
         <v>502</v>
       </c>
-      <c r="AA259" s="3" t="s">
+      <c r="AA259" t="s">
         <v>503</v>
       </c>
-      <c r="AB259" s="3" t="s">
+      <c r="AB259" t="s">
         <v>504</v>
       </c>
-      <c r="AC259" s="3" t="s">
+      <c r="AC259" t="s">
         <v>505</v>
       </c>
-      <c r="AD259" s="3" t="s">
+      <c r="AD259" t="s">
         <v>506</v>
       </c>
-      <c r="AE259" s="3" t="s">
+      <c r="AE259" t="s">
         <v>503</v>
       </c>
-      <c r="AF259" s="3"/>
     </row>
     <row r="260" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
@@ -32689,9 +32674,7 @@
       <c r="AE268" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="AF268" s="2">
-        <v>1</v>
-      </c>
+      <c r="AF268" s="2"/>
     </row>
     <row r="269" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
@@ -35328,102 +35311,99 @@
         <v>1732</v>
       </c>
     </row>
-    <row r="297" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A297" s="2" t="s">
+    <row r="297" spans="1:32" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A297" s="3" t="s">
         <v>1755</v>
       </c>
-      <c r="B297" s="2" t="s">
+      <c r="B297" s="3" t="s">
         <v>663</v>
       </c>
-      <c r="C297" s="2">
+      <c r="C297" s="3">
         <v>1.8713035307585831E-2</v>
       </c>
-      <c r="D297" s="2">
+      <c r="D297" s="3">
         <v>6.570775484371552</v>
       </c>
-      <c r="E297" s="2">
+      <c r="E297" s="3">
         <v>0.14894494124842431</v>
       </c>
-      <c r="F297" s="2">
+      <c r="F297" s="3">
         <v>2.422062764933798</v>
       </c>
-      <c r="G297" s="2">
+      <c r="G297" s="3">
         <v>2.1307439820366092E-3</v>
       </c>
-      <c r="H297" s="2">
+      <c r="H297" s="3">
         <v>18.759533762822681</v>
       </c>
-      <c r="I297" s="2">
+      <c r="I297" s="3">
         <v>0.12621747006101239</v>
       </c>
-      <c r="J297" s="2">
+      <c r="J297" s="3">
         <v>0.1056989320410896</v>
       </c>
-      <c r="K297" s="2">
+      <c r="K297" s="3">
         <v>3.2404373173188117E-2</v>
       </c>
-      <c r="L297" s="2">
+      <c r="L297" s="3">
         <v>0.13008006438259151</v>
       </c>
-      <c r="M297" s="2">
+      <c r="M297" s="3">
         <v>3.938709224528851E-2</v>
       </c>
-      <c r="N297" s="2">
+      <c r="N297" s="3">
         <v>0.86139218923705252</v>
       </c>
-      <c r="O297" s="2">
+      <c r="O297" s="3">
         <v>4.9127610130162394</v>
       </c>
-      <c r="P297" s="2">
+      <c r="P297" s="3">
         <v>8.52774638035593E-3</v>
       </c>
-      <c r="Q297" s="2">
+      <c r="Q297" s="3">
         <v>2.7059580588423341E-2</v>
       </c>
-      <c r="R297" s="2">
+      <c r="R297" s="3">
         <v>0.99669340247992355</v>
       </c>
-      <c r="S297" s="2">
+      <c r="S297" s="3">
         <v>0.8629608621156204</v>
       </c>
-      <c r="T297" s="2">
-        <v>0</v>
-      </c>
-      <c r="U297" s="2">
+      <c r="T297" s="3">
+        <v>0</v>
+      </c>
+      <c r="U297" s="3">
         <v>5.067616983171324</v>
       </c>
-      <c r="V297" s="2">
+      <c r="V297" s="3">
         <v>3.306597520076449E-3</v>
       </c>
-      <c r="W297" s="2">
+      <c r="W297" s="3">
         <v>8.0037676511799605E-2</v>
       </c>
-      <c r="X297" s="2">
+      <c r="X297" s="3">
         <v>4.3726675195606947E-2</v>
       </c>
-      <c r="Y297" s="2" t="s">
+      <c r="Y297" s="3" t="s">
         <v>1756</v>
       </c>
-      <c r="Z297" s="2" t="s">
+      <c r="Z297" s="3" t="s">
         <v>1757</v>
       </c>
-      <c r="AA297" s="2" t="s">
+      <c r="AA297" s="3" t="s">
         <v>1758</v>
       </c>
-      <c r="AB297" s="2" t="s">
+      <c r="AB297" s="3" t="s">
         <v>1759</v>
       </c>
-      <c r="AC297" s="2" t="s">
+      <c r="AC297" s="3" t="s">
         <v>1760</v>
       </c>
-      <c r="AD297" s="2" t="s">
+      <c r="AD297" s="3" t="s">
         <v>1761</v>
       </c>
-      <c r="AE297" s="2" t="s">
+      <c r="AE297" s="3" t="s">
         <v>1758</v>
-      </c>
-      <c r="AF297" s="2">
-        <v>1</v>
       </c>
     </row>
     <row r="298" spans="1:32" x14ac:dyDescent="0.2">
@@ -37669,9 +37649,7 @@
       <c r="AE321" s="2" t="s">
         <v>1329</v>
       </c>
-      <c r="AF321" s="2">
-        <v>1</v>
-      </c>
+      <c r="AF321" s="2"/>
     </row>
     <row r="322" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A322" t="s">
